--- a/AAII_Financials/Quarterly/UOVEY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UOVEY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="92">
   <si>
     <t>UOVEY</t>
   </si>
@@ -656,129 +656,132 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44926</v>
       </c>
       <c r="K7" s="2">
         <v>44926</v>
       </c>
       <c r="L7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -815,68 +818,71 @@
       <c r="N8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P8" s="3">
         <v>3199200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3009400</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S8" s="3">
+      <c r="S8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T8" s="3">
         <v>1839100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2134500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2175700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2364000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2409300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2298200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2269900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2060300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1924800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1771200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1759700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1710700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1641300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1581600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1543500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1493300</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -973,8 +979,11 @@
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1071,8 +1080,11 @@
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1107,8 +1119,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1205,8 +1218,11 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1303,8 +1319,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1341,8 +1360,8 @@
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1401,8 +1420,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1448,8 +1470,8 @@
       <c r="Q15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="R15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1499,8 +1521,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1532,8 +1557,9 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1570,68 +1596,71 @@
       <c r="N17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P17" s="3">
         <v>881700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>986800</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S17" s="3">
+      <c r="S17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T17" s="3">
         <v>1052400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1167800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1109200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1233300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1200900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1190600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1163800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>999100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>900300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>768000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>786000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>835400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>774200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>757300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>705000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>728000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1668,68 +1697,71 @@
       <c r="N18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P18" s="3">
         <v>2317500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2022600</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T18" s="3">
         <v>786700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>966700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1066500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1130700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1208400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1107600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1106000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1061200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1024500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1003200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>973700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>875200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>867100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>824400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>838500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>765300</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1764,8 +1796,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1802,68 +1835,71 @@
       <c r="N20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3">
         <v>-396100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-207900</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T20" s="3">
         <v>-158800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-188500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-214300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-159800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-150100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-175700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-281000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-182000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-119900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-142200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-172400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-84100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-105400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-75900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-164800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-60800</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1900,68 +1936,71 @@
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>2298300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1652800</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3">
         <v>793400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>564200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>930000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1045600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1131500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>999300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>879500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>927800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>951800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>907300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>853100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>837600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>805200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>797100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>716700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>744800</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1998,8 +2037,8 @@
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2058,8 +2097,11 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2096,68 +2138,71 @@
       <c r="N23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P23" s="3">
         <v>1921400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1814700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>627400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>593700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>627900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>778300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>852200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>970800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1058300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>931900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>825000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>879100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>904500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>861100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>801300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>791200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>761700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>748400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>673700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>704600</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2194,68 +2239,71 @@
       <c r="N24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P24" s="3">
         <v>326000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>317000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>100300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>98000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>104600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>144100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>127800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>148100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>174200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>148300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>138500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>145300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>142500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>153000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>166700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>137900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>135700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>149700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>129600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>123800</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2352,8 +2400,11 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2390,68 +2441,71 @@
       <c r="N26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P26" s="3">
         <v>1595400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1497600</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S26" s="3">
+      <c r="S26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T26" s="3">
         <v>523200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>634100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>724300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>822700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>884100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>783600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>686600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>733800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>762000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>708000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>634600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>653300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>626000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>598700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>544100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>580800</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2488,68 +2542,71 @@
       <c r="N27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P27" s="3">
         <v>1535300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1493200</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S27" s="3">
+      <c r="S27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T27" s="3">
         <v>521700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>632700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>650100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>819800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>881000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>779900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>601400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>731700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>759900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>705900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>555200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>651100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>623100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>595800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>473700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>579300</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2646,8 +2703,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2684,8 +2744,8 @@
       <c r="N29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -2744,8 +2804,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2842,8 +2905,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2940,8 +3006,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2978,68 +3047,71 @@
       <c r="N32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3">
         <v>396100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>207900</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T32" s="3">
         <v>158800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>188500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>214300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>159800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>150100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>175700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>281000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>182000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>119900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>142200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>172400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>84100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>105400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>75900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>164800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>60800</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3076,68 +3148,71 @@
       <c r="N33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P33" s="3">
         <v>1535300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1493200</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S33" s="3">
+      <c r="S33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T33" s="3">
         <v>521700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>632700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>650100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>819800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>881000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>779900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>601400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>731700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>759900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>705900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>555200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>651100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>623100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>595800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>473700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>579300</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3234,8 +3309,11 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3272,171 +3350,177 @@
       <c r="N35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P35" s="3">
         <v>1535300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1493200</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S35" s="3">
+      <c r="S35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T35" s="3">
         <v>521700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>632700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>650100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>819800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>881000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>779900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>601400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>731700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>759900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>705900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>555200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>651100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>623100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>595800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>473700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>579300</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44926</v>
       </c>
       <c r="K38" s="2">
         <v>44926</v>
       </c>
       <c r="L38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3471,8 +3555,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3507,233 +3592,240 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>24032300</v>
+      </c>
+      <c r="E41" s="3">
         <v>22478900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>22387400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>23304600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>21968000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>34646300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>35778100</v>
-      </c>
-      <c r="J41" s="3">
-        <v>32264400</v>
       </c>
       <c r="K41" s="3">
         <v>32264400</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="L41" s="3">
+        <v>32264400</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N41" s="3">
         <v>35778100</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P41" s="3">
         <v>58168600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>56027600</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S41" s="3">
+      <c r="S41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T41" s="3">
         <v>56398200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>62159000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>56350000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>54343400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>60228700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>58529500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>56823000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>55972200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>61652000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>55633300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>58107600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>57352600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>55610200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>50503300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>47133000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>44354300</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>40137900</v>
+      </c>
+      <c r="E42" s="3">
         <v>38409100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>35064200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>39095800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>36036900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>37168400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>33002800</v>
-      </c>
-      <c r="J42" s="3">
-        <v>40136900</v>
       </c>
       <c r="K42" s="3">
         <v>40136900</v>
       </c>
       <c r="L42" s="3">
-        <v>0</v>
+        <v>40136900</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>33002800</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>26863900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>23984200</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S42" s="3">
+      <c r="S42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T42" s="3">
         <v>17594600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>14395500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>13061200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>13128100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>12759300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>12732500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>11567200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>10260400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>9848300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>9675900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>9614300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>10128200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>9724900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>10082500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>10815200</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>11601100</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3">
         <v>1389300</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F43" s="3">
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3">
         <v>1464700</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3">
         <v>1787200</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J43" s="3">
-        <v>2059900</v>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K43" s="3">
         <v>2059900</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>5</v>
+      <c r="L43" s="3">
+        <v>2059900</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>5</v>
@@ -3741,8 +3833,8 @@
       <c r="N43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -3801,46 +3893,49 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E44" s="3">
         <v>15500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>35300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>58600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>47200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>68900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>66500</v>
-      </c>
-      <c r="J44" s="3">
-        <v>70100</v>
       </c>
       <c r="K44" s="3">
         <v>70100</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="L44" s="3">
+        <v>70100</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N44" s="3">
         <v>66500</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3899,37 +3994,40 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3">
         <v>1977900</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3">
         <v>1722700</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3">
         <v>2029600</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J45" s="3">
-        <v>1549000</v>
+      <c r="J45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K45" s="3">
         <v>1549000</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>5</v>
+      <c r="L45" s="3">
+        <v>1549000</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>5</v>
@@ -3937,8 +4035,8 @@
       <c r="N45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
+      <c r="O45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P45" s="3">
         <v>0</v>
@@ -3997,46 +4095,49 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>69855300</v>
+      </c>
+      <c r="E46" s="3">
         <v>69580100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>62732900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>70608500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>62732600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>80715000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>73691800</v>
-      </c>
-      <c r="J46" s="3">
-        <v>80672100</v>
       </c>
       <c r="K46" s="3">
         <v>80672100</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="L46" s="3">
+        <v>80672100</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N46" s="3">
         <v>73691800</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O46" s="3">
-        <v>0</v>
+      <c r="O46" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P46" s="3">
         <v>0</v>
@@ -4095,302 +4196,314 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>93341300</v>
+      </c>
+      <c r="E47" s="3">
         <v>90020400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>78309200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>68022000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>65329300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>65214300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>54547300</v>
-      </c>
-      <c r="J47" s="3">
-        <v>50951600</v>
       </c>
       <c r="K47" s="3">
         <v>50951600</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="L47" s="3">
+        <v>50951600</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N47" s="3">
         <v>54547300</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P47" s="3">
         <v>959500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>913300</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S47" s="3">
+      <c r="S47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T47" s="3">
         <v>888400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>899500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>846600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>867400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>888600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>877000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>873900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>891800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>883400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>874800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>880400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>867900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>850900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>844300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>812200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>801200</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4002000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3724800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3562300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3054800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2891700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2865300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2646800</v>
-      </c>
-      <c r="J48" s="3">
-        <v>2575200</v>
       </c>
       <c r="K48" s="3">
         <v>2575200</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="L48" s="3">
+        <v>2575200</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3">
         <v>2646800</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P48" s="3">
         <v>3091300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2933600</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S48" s="3">
+      <c r="S48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T48" s="3">
         <v>2804700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2776100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2645800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2668300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2698200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2614000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2449200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2257100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2229600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2231000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2255600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2236400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2221600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2201000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2189700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2127600</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3787200</v>
+      </c>
+      <c r="E49" s="3">
         <v>3850800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3879500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3648300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3641900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3775900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3614000</v>
-      </c>
-      <c r="J49" s="3">
-        <v>3654400</v>
       </c>
       <c r="K49" s="3">
         <v>3654400</v>
       </c>
       <c r="L49" s="3">
-        <v>0</v>
+        <v>3654400</v>
       </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>3614000</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
         <v>3194600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3076900</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S49" s="3">
+      <c r="S49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T49" s="3">
         <v>3077800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3055400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2969700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3041500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3125100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3069100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3092000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2918200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2919600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2988100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3054100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3055600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3057800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3058500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3040200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3037200</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4487,8 +4600,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4585,77 +4701,80 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8521800</v>
+      </c>
+      <c r="E52" s="3">
         <v>6569600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7154400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3468000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7120800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3317600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6061300</v>
-      </c>
-      <c r="J52" s="3">
-        <v>2612500</v>
       </c>
       <c r="K52" s="3">
         <v>2612500</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="L52" s="3">
+        <v>2612500</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N52" s="3">
         <v>6061300</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P52" s="3">
         <v>393100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>331200</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S52" s="3">
+      <c r="S52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T52" s="3">
         <v>316200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>265300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>214500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>211900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>196100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>200200</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>5</v>
       </c>
@@ -4665,26 +4784,29 @@
       <c r="AB52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AC52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD52" s="3">
         <v>142500</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AG52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH52" s="3">
         <v>183900</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4781,106 +4903,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>456090400</v>
+      </c>
+      <c r="E54" s="3">
         <v>444757900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>422380300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>393965200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>381188500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>396624100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>373566900</v>
-      </c>
-      <c r="J54" s="3">
-        <v>376072100</v>
       </c>
       <c r="K54" s="3">
         <v>376072100</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="L54" s="3">
+        <v>376072100</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N54" s="3">
         <v>373566900</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P54" s="3">
         <v>354004800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>331530700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>323286200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>313254400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>318846600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>316802700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>289544400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>299446800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>306542100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>296882200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>289967100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>269977900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>271124400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>263049000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>264407800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>261127300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>253953700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>252596900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>249032800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>240096500</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4915,8 +5043,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4951,46 +5080,47 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>364046600</v>
+      </c>
+      <c r="E57" s="3">
         <v>353494300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>336302700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>310469300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>305720700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>316559800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>296145800</v>
-      </c>
-      <c r="J57" s="3">
-        <v>293162600</v>
       </c>
       <c r="K57" s="3">
         <v>293162600</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="L57" s="3">
+        <v>293162600</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N57" s="3">
         <v>296145800</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O57" s="3">
-        <v>0</v>
+      <c r="O57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P57" s="3">
         <v>0</v>
@@ -5049,44 +5179,47 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>25677500</v>
+      </c>
+      <c r="E58" s="3">
         <v>22957800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>23557500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>21258100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>22050600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>18667500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>20678500</v>
-      </c>
-      <c r="J58" s="3">
-        <v>24882500</v>
       </c>
       <c r="K58" s="3">
         <v>24882500</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>24882500</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>20678500</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
@@ -5147,77 +5280,80 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1482900</v>
+      </c>
+      <c r="E59" s="3">
         <v>914300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1358600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1037600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1232700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1370500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1296800</v>
-      </c>
-      <c r="J59" s="3">
-        <v>1185800</v>
       </c>
       <c r="K59" s="3">
         <v>1185800</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="L59" s="3">
+        <v>1185800</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N59" s="3">
         <v>1296800</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P59" s="3">
         <v>433900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>340100</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T59" s="3">
         <v>482400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>422000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>350100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>341700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>408800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>472200</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5227,64 +5363,67 @@
       <c r="AB59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD59" s="3">
         <v>405900</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH59" s="3">
         <v>305700</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>391206900</v>
+      </c>
+      <c r="E60" s="3">
         <v>379430600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>361218800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>335174200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>329003900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>339617700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>318121100</v>
-      </c>
-      <c r="J60" s="3">
-        <v>321355000</v>
       </c>
       <c r="K60" s="3">
         <v>321355000</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="L60" s="3">
+        <v>321355000</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N60" s="3">
         <v>318121100</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O60" s="3">
-        <v>0</v>
+      <c r="O60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P60" s="3">
         <v>0</v>
@@ -5343,175 +5482,181 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>16804900</v>
+      </c>
+      <c r="E61" s="3">
         <v>20758300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>14945600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18425400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10393100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>17934100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>15088600</v>
-      </c>
-      <c r="J61" s="3">
-        <v>17676000</v>
       </c>
       <c r="K61" s="3">
         <v>17676000</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>17676000</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>15088600</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>26247300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>22903900</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>17798000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>14608300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>18049200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>20256000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>23638900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>16651200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>22867300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>16867400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>19583800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>17617400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>18565000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>18916700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>19631900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>19255900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>19146800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>14199600</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6736000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4265200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6244900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3525900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6131600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3478900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6096800</v>
-      </c>
-      <c r="J62" s="3">
-        <v>4251700</v>
       </c>
       <c r="K62" s="3">
         <v>4251700</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="L62" s="3">
+        <v>4251700</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N62" s="3">
         <v>6096800</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P62" s="3">
         <v>332200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>314100</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S62" s="3">
+      <c r="S62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T62" s="3">
         <v>331700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>292700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>214200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>226600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>203700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>195700</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>5</v>
       </c>
@@ -5521,26 +5666,29 @@
       <c r="AB62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AC62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD62" s="3">
         <v>131200</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AG62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH62" s="3">
         <v>169800</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5637,8 +5785,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5735,8 +5886,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5833,106 +5987,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>414980400</v>
+      </c>
+      <c r="E66" s="3">
         <v>404723900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>382663800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>357360000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>346106200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>361419500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>339628600</v>
-      </c>
-      <c r="J66" s="3">
-        <v>343551200</v>
       </c>
       <c r="K66" s="3">
         <v>343551200</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="L66" s="3">
+        <v>343551200</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N66" s="3">
         <v>339628600</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P66" s="3">
         <v>321147100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>300322700</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S66" s="3">
+      <c r="S66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T66" s="3">
         <v>289099700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>287032400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>261165900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>270495900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>277098700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>267978100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>261856600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>244034800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>244552700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>235710900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>237236500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>235211700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>228403000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>227719500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>224956800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>216354600</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5967,8 +6127,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6065,8 +6226,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6163,47 +6327,50 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>2663600</v>
+      </c>
+      <c r="E70" s="3">
         <v>2136500</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>2158100</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>2013600</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>2027100</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>2081900</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>2680000</v>
-      </c>
-      <c r="J70" s="3">
-        <v>2071100</v>
       </c>
       <c r="K70" s="3">
         <v>2071100</v>
       </c>
       <c r="L70" s="3">
+        <v>2071100</v>
+      </c>
+      <c r="M70" s="3">
         <v>2656200</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>2680000</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>2088400</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -6261,8 +6428,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6359,106 +6529,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>28309500</v>
+      </c>
+      <c r="E72" s="3">
         <v>32692400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>27495200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>30658400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>24515900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>29392200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>22556800</v>
-      </c>
-      <c r="J72" s="3">
-        <v>26768600</v>
       </c>
       <c r="K72" s="3">
         <v>26768600</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="L72" s="3">
+        <v>26768600</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N72" s="3">
         <v>22556800</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P72" s="3">
         <v>27161400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>25623700</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T72" s="3">
         <v>24289700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>24370300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>23133900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>23216200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>24108800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>23704300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>22869800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>20963200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>20949800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>21760300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>21445100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>20844100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>20533000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>20193100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>19424600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>19098500</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6555,8 +6731,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6653,8 +6832,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6751,106 +6933,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>38253900</v>
+      </c>
+      <c r="E76" s="3">
         <v>37707100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>37380100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>34427600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>32896600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>32939400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>31080100</v>
-      </c>
-      <c r="J76" s="3">
-        <v>30270900</v>
       </c>
       <c r="K76" s="3">
         <v>30270900</v>
       </c>
       <c r="L76" s="3">
+        <v>30270900</v>
+      </c>
+      <c r="M76" s="3">
         <v>30803400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>31080100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>30523800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>32857700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>31208000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>30621400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>29676400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>29746900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>29770200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>28378600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>28950900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>29443400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>28904100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>28110500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>25943100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>26571800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>27338100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>27171300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>25915600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>25550700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>24877500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>24076000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>23741900</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6947,111 +7135,117 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44926</v>
       </c>
       <c r="K80" s="2">
         <v>44926</v>
       </c>
       <c r="L80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7088,68 +7282,71 @@
       <c r="N81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P81" s="3">
         <v>1535300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1493200</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S81" s="3">
+      <c r="S81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T81" s="3">
         <v>521700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>632700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>650100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>819800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>881000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>779900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>601400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>731700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>759900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>705900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>555200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>651100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>623100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>595800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>473700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>579300</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7184,8 +7381,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7222,68 +7420,71 @@
       <c r="N83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>376900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>-161900</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
         <v>165500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>-214100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>77800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>74800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>73200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>67500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>54400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>48700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>47300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>46200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>51800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>46500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>43500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>48700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>43000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>40300</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7380,8 +7581,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7478,8 +7682,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7576,8 +7783,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7674,8 +7884,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7772,8 +7985,11 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7810,68 +8026,71 @@
       <c r="N89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3">
         <v>-2164900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7080500</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
         <v>6183000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>987700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4978600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-485400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-8230400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>9601800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-4385900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>466400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-137600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1240700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-3012900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3652800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>889200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1353000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-6645300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-370600</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7906,8 +8125,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7944,68 +8164,71 @@
       <c r="N91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P91" s="3">
         <v>-257000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-302000</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-118000</v>
       </c>
       <c r="R91" s="3">
         <v>-118000</v>
       </c>
       <c r="S91" s="3">
+        <v>-118000</v>
+      </c>
+      <c r="T91" s="3">
         <v>-143000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>317800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-118100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-101200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-105600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-96400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-118400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-87500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-106500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-59900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-71100</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>-63400</v>
       </c>
       <c r="AE91" s="3">
         <v>-63400</v>
       </c>
       <c r="AF91" s="3">
+        <v>-63400</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-59700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-92900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-56400</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8102,8 +8325,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8200,8 +8426,11 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8238,68 +8467,71 @@
       <c r="N94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>-339100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>240600</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
         <v>-163300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>269900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-101000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-88000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-90500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-88200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-32900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-79700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-86100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-59900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-73700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-64900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-54600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-58300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-107600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-35900</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8334,8 +8566,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8372,45 +8605,45 @@
       <c r="N96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O96" s="3">
+      <c r="O96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P96" s="3">
         <v>-1238500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>918500</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-929200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>1540900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-673100</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>400</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-589200</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
         <v>0</v>
       </c>
@@ -8418,22 +8651,25 @@
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-390800</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-99500</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-300</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-93700</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8530,8 +8766,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8628,8 +8867,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8726,8 +8968,11 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8764,68 +9009,71 @@
       <c r="N100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>2329100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1090000</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
         <v>-2293300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1241800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2002700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2957900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>5676300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-6147900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>4950400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-3951200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1536000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-393400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>410600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1062500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>243300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>148900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>4704400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>686200</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8862,68 +9110,71 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
         <v>125600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>38600</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
         <v>551400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>351500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-101300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>206800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>134300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>14100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>9200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>33200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>255400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-281500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-160300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-65600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>17000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-264000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>266600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-382300</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8951,8 +9202,8 @@
       <c r="K102" s="3">
         <v>0</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>5</v>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>5</v>
@@ -8960,64 +9211,67 @@
       <c r="N102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3">
         <v>-302100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7891300</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
         <v>4277900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2850800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2773500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3324600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2510400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3379800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>540800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3531400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1567800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>506000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2836200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>2459800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1095000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1179800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1781900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-102500</v>
       </c>
     </row>
